--- a/src/BACKUP/DER OPS NEW CRM 2022 (Only commo).xlsx
+++ b/src/BACKUP/DER OPS NEW CRM 2022 (Only commo).xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omimr\mon-crm\src\BACKUP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FFB03EB-244D-4DF2-A975-FD96986E3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABFFE2D-18F4-4986-835A-207690BC5B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{9E7021B6-78C1-4C7A-AF7C-40194427DF90}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E7021B6-78C1-4C7A-AF7C-40194427DF90}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$T$527</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5658" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5683" uniqueCount="208">
   <si>
     <t>ref</t>
   </si>
@@ -658,6 +661,9 @@
   <si>
     <t>CTR21624-corn-336.91/2</t>
   </si>
+  <si>
+    <t>C4359</t>
+  </si>
 </sst>
 </file>
 
@@ -14829,8 +14835,8 @@
       <c r="M263" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N263" s="2">
-        <v>4359</v>
+      <c r="N263" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O263" s="2" t="s">
         <v>81</v>
@@ -14876,8 +14882,8 @@
       <c r="M264" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N264" s="2">
-        <v>4359</v>
+      <c r="N264" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O264" s="2" t="s">
         <v>81</v>
@@ -14923,8 +14929,8 @@
       <c r="M265" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N265" s="2">
-        <v>4359</v>
+      <c r="N265" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O265" s="2" t="s">
         <v>81</v>
@@ -14970,8 +14976,8 @@
       <c r="M266" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N266" s="2">
-        <v>4359</v>
+      <c r="N266" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O266" s="2" t="s">
         <v>81</v>
@@ -15017,8 +15023,8 @@
       <c r="M267" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N267" s="2">
-        <v>4359</v>
+      <c r="N267" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O267" s="2" t="s">
         <v>81</v>
@@ -15064,8 +15070,8 @@
       <c r="M268" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N268" s="2">
-        <v>4359</v>
+      <c r="N268" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O268" s="2" t="s">
         <v>81</v>
@@ -15111,8 +15117,8 @@
       <c r="M269" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N269" s="2">
-        <v>4359</v>
+      <c r="N269" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O269" s="2" t="s">
         <v>81</v>
@@ -15158,8 +15164,8 @@
       <c r="M270" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N270" s="2">
-        <v>4359</v>
+      <c r="N270" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O270" s="2" t="s">
         <v>81</v>
@@ -15205,8 +15211,8 @@
       <c r="M271" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N271" s="2">
-        <v>4359</v>
+      <c r="N271" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O271" s="2" t="s">
         <v>81</v>
@@ -15252,8 +15258,8 @@
       <c r="M272" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N272" s="2">
-        <v>4359</v>
+      <c r="N272" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O272" s="2" t="s">
         <v>81</v>
@@ -15299,8 +15305,8 @@
       <c r="M273" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N273" s="2">
-        <v>4359</v>
+      <c r="N273" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O273" s="2" t="s">
         <v>81</v>
@@ -15346,8 +15352,8 @@
       <c r="M274" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N274" s="2">
-        <v>4359</v>
+      <c r="N274" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O274" s="2" t="s">
         <v>81</v>
@@ -15393,8 +15399,8 @@
       <c r="M275" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N275" s="2">
-        <v>4359</v>
+      <c r="N275" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O275" s="2" t="s">
         <v>81</v>
@@ -15440,8 +15446,8 @@
       <c r="M276" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N276" s="2">
-        <v>4359</v>
+      <c r="N276" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O276" s="2" t="s">
         <v>81</v>
@@ -15487,8 +15493,8 @@
       <c r="M277" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N277" s="2">
-        <v>4359</v>
+      <c r="N277" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O277" s="2" t="s">
         <v>81</v>
@@ -15534,8 +15540,8 @@
       <c r="M278" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N278" s="2">
-        <v>4359</v>
+      <c r="N278" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O278" s="2" t="s">
         <v>81</v>
@@ -15581,8 +15587,8 @@
       <c r="M279" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N279" s="2">
-        <v>4359</v>
+      <c r="N279" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O279" s="2" t="s">
         <v>81</v>
@@ -15628,8 +15634,8 @@
       <c r="M280" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N280" s="2">
-        <v>4359</v>
+      <c r="N280" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O280" s="2" t="s">
         <v>81</v>
@@ -15728,8 +15734,8 @@
       <c r="M282" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N282" s="2">
-        <v>4359</v>
+      <c r="N282" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O282" s="2" t="s">
         <v>81</v>
@@ -15775,8 +15781,8 @@
       <c r="M283" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N283" s="2">
-        <v>4359</v>
+      <c r="N283" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O283" s="2" t="s">
         <v>81</v>
@@ -15822,8 +15828,8 @@
       <c r="M284" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N284" s="2">
-        <v>4359</v>
+      <c r="N284" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O284" s="2" t="s">
         <v>81</v>
@@ -15869,8 +15875,8 @@
       <c r="M285" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N285" s="2">
-        <v>4359</v>
+      <c r="N285" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O285" s="2" t="s">
         <v>81</v>
@@ -15916,8 +15922,8 @@
       <c r="M286" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N286" s="2">
-        <v>4359</v>
+      <c r="N286" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O286" s="2" t="s">
         <v>81</v>
@@ -15963,8 +15969,8 @@
       <c r="M287" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N287" s="2">
-        <v>4359</v>
+      <c r="N287" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O287" s="2" t="s">
         <v>81</v>
@@ -16010,8 +16016,8 @@
       <c r="M288" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N288" s="2">
-        <v>4359</v>
+      <c r="N288" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="O288" s="2" t="s">
         <v>81</v>
